--- a/informes_data/Euroleague/2025-26/playoffs/aggregate_individual/AGG_IND_REAL MADRID.xlsx
+++ b/informes_data/Euroleague/2025-26/playoffs/aggregate_individual/AGG_IND_REAL MADRID.xlsx
@@ -553,7 +553,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>T. LYLES</t>
+          <t>T. MALEDON</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -565,73 +565,73 @@
         <v>6</v>
       </c>
       <c r="D2" t="n">
-        <v>17.6294</v>
+        <v>16.4007</v>
       </c>
       <c r="E2" t="n">
-        <v>8.672000000000001</v>
+        <v>10.7391</v>
       </c>
       <c r="F2" t="n">
-        <v>8.957600000000001</v>
+        <v>5.6616</v>
       </c>
       <c r="G2" t="n">
-        <v>3.399</v>
+        <v>7.6685</v>
       </c>
       <c r="H2" t="n">
-        <v>-3.287</v>
+        <v>2.9615</v>
       </c>
       <c r="I2" t="n">
-        <v>6.6861</v>
+        <v>4.7071</v>
       </c>
       <c r="J2" t="n">
-        <v>7.8953</v>
+        <v>8.262</v>
       </c>
       <c r="K2" t="n">
-        <v>-1.2223</v>
+        <v>2.2359</v>
       </c>
       <c r="L2" t="n">
-        <v>9.1175</v>
+        <v>6.0261</v>
       </c>
       <c r="M2" t="n">
-        <v>-4.4963</v>
+        <v>-0.5932999999999999</v>
       </c>
       <c r="N2" t="n">
-        <v>-2.0647</v>
+        <v>0.7258</v>
       </c>
       <c r="O2" t="n">
-        <v>-2.4316</v>
+        <v>-1.319</v>
       </c>
       <c r="P2" t="n">
-        <v>7.2791</v>
+        <v>-0.2274000000000001</v>
       </c>
       <c r="Q2" t="n">
-        <v>-2.5023</v>
+        <v>-7.051600000000001</v>
       </c>
       <c r="R2" t="n">
-        <v>9.7814</v>
+        <v>6.8243</v>
       </c>
       <c r="S2" t="n">
-        <v>6.0197</v>
+        <v>2.0321</v>
       </c>
       <c r="T2" t="n">
-        <v>0.6234999999999999</v>
+        <v>0.3328</v>
       </c>
       <c r="U2" t="n">
-        <v>5.396</v>
+        <v>1.6994</v>
       </c>
       <c r="V2" t="n">
-        <v>0.9318</v>
+        <v>6.9274</v>
       </c>
       <c r="W2" t="n">
-        <v>2.6552</v>
+        <v>9.196</v>
       </c>
       <c r="X2" t="n">
-        <v>-1.7234</v>
+        <v>-2.2685</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>U. GARUBA</t>
+          <t>T. LYLES</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -640,76 +640,76 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D3" t="n">
-        <v>16.9813</v>
+        <v>16.2852</v>
       </c>
       <c r="E3" t="n">
-        <v>11.6886</v>
+        <v>8.438499999999999</v>
       </c>
       <c r="F3" t="n">
-        <v>5.2928</v>
+        <v>7.846700000000001</v>
       </c>
       <c r="G3" t="n">
-        <v>10.0249</v>
+        <v>3.399</v>
       </c>
       <c r="H3" t="n">
-        <v>7.6814</v>
+        <v>-3.287</v>
       </c>
       <c r="I3" t="n">
-        <v>2.3434</v>
+        <v>6.6861</v>
       </c>
       <c r="J3" t="n">
-        <v>9.1464</v>
+        <v>7.8953</v>
       </c>
       <c r="K3" t="n">
-        <v>7.507300000000001</v>
+        <v>-1.2223</v>
       </c>
       <c r="L3" t="n">
-        <v>1.6391</v>
+        <v>9.1175</v>
       </c>
       <c r="M3" t="n">
-        <v>0.8787</v>
+        <v>-4.4963</v>
       </c>
       <c r="N3" t="n">
-        <v>0.1743</v>
+        <v>-2.0647</v>
       </c>
       <c r="O3" t="n">
-        <v>0.7043999999999999</v>
+        <v>-2.4316</v>
       </c>
       <c r="P3" t="n">
-        <v>2.2747</v>
+        <v>7.2791</v>
       </c>
       <c r="Q3" t="n">
-        <v>-3.4122</v>
+        <v>-2.5023</v>
       </c>
       <c r="R3" t="n">
-        <v>5.6869</v>
+        <v>9.7814</v>
       </c>
       <c r="S3" t="n">
-        <v>6.1585</v>
+        <v>4.6752</v>
       </c>
       <c r="T3" t="n">
-        <v>4.7059</v>
+        <v>0.3902000000000002</v>
       </c>
       <c r="U3" t="n">
-        <v>1.4526</v>
+        <v>4.2851</v>
       </c>
       <c r="V3" t="n">
-        <v>-1.4769</v>
+        <v>0.9318</v>
       </c>
       <c r="W3" t="n">
-        <v>1.2485</v>
+        <v>2.6552</v>
       </c>
       <c r="X3" t="n">
-        <v>-2.7253</v>
+        <v>-1.7234</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>T. MALEDON</t>
+          <t>U. GARUBA</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -718,70 +718,70 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D4" t="n">
-        <v>14.4425</v>
+        <v>14.9592</v>
       </c>
       <c r="E4" t="n">
-        <v>9.221499999999999</v>
+        <v>9.425599999999999</v>
       </c>
       <c r="F4" t="n">
-        <v>5.221</v>
+        <v>5.5335</v>
       </c>
       <c r="G4" t="n">
-        <v>7.6685</v>
+        <v>10.0249</v>
       </c>
       <c r="H4" t="n">
-        <v>2.9615</v>
+        <v>7.6814</v>
       </c>
       <c r="I4" t="n">
-        <v>4.7071</v>
+        <v>2.3434</v>
       </c>
       <c r="J4" t="n">
-        <v>8.262</v>
+        <v>9.1464</v>
       </c>
       <c r="K4" t="n">
-        <v>2.2359</v>
+        <v>7.507300000000001</v>
       </c>
       <c r="L4" t="n">
-        <v>6.0261</v>
+        <v>1.6391</v>
       </c>
       <c r="M4" t="n">
-        <v>-0.5932999999999999</v>
+        <v>0.8787</v>
       </c>
       <c r="N4" t="n">
-        <v>0.7258</v>
+        <v>0.1743</v>
       </c>
       <c r="O4" t="n">
-        <v>-1.319</v>
+        <v>0.7043999999999999</v>
       </c>
       <c r="P4" t="n">
-        <v>-0.2274000000000001</v>
+        <v>2.2747</v>
       </c>
       <c r="Q4" t="n">
-        <v>-7.051600000000001</v>
+        <v>-3.4122</v>
       </c>
       <c r="R4" t="n">
-        <v>6.8243</v>
+        <v>5.6869</v>
       </c>
       <c r="S4" t="n">
-        <v>0.07419999999999982</v>
+        <v>4.1363</v>
       </c>
       <c r="T4" t="n">
-        <v>-1.1848</v>
+        <v>2.4429</v>
       </c>
       <c r="U4" t="n">
-        <v>1.2588</v>
+        <v>1.6933</v>
       </c>
       <c r="V4" t="n">
-        <v>6.9274</v>
+        <v>-1.4769</v>
       </c>
       <c r="W4" t="n">
-        <v>9.196</v>
+        <v>1.2485</v>
       </c>
       <c r="X4" t="n">
-        <v>-2.2685</v>
+        <v>-2.7253</v>
       </c>
     </row>
     <row r="5">
@@ -799,13 +799,13 @@
         <v>6</v>
       </c>
       <c r="D5" t="n">
-        <v>9.3301</v>
+        <v>8.591899999999999</v>
       </c>
       <c r="E5" t="n">
-        <v>1.7725</v>
+        <v>0.7937</v>
       </c>
       <c r="F5" t="n">
-        <v>7.5575</v>
+        <v>7.7984</v>
       </c>
       <c r="G5" t="n">
         <v>3.2091</v>
@@ -844,13 +844,13 @@
         <v>10.0088</v>
       </c>
       <c r="S5" t="n">
-        <v>4.2548</v>
+        <v>3.5167</v>
       </c>
       <c r="T5" t="n">
-        <v>2.8383</v>
+        <v>1.8595</v>
       </c>
       <c r="U5" t="n">
-        <v>1.4165</v>
+        <v>1.6572</v>
       </c>
       <c r="V5" t="n">
         <v>-1.3186</v>
@@ -877,13 +877,13 @@
         <v>6</v>
       </c>
       <c r="D6" t="n">
-        <v>6.833500000000001</v>
+        <v>5.289099999999999</v>
       </c>
       <c r="E6" t="n">
-        <v>4.858199999999999</v>
+        <v>2.3618</v>
       </c>
       <c r="F6" t="n">
-        <v>1.9755</v>
+        <v>2.9273</v>
       </c>
       <c r="G6" t="n">
         <v>-0.5977999999999999</v>
@@ -922,13 +922,13 @@
         <v>7.734</v>
       </c>
       <c r="S6" t="n">
-        <v>1.8319</v>
+        <v>0.2874999999999999</v>
       </c>
       <c r="T6" t="n">
-        <v>3.4012</v>
+        <v>0.9047999999999999</v>
       </c>
       <c r="U6" t="n">
-        <v>-1.5691</v>
+        <v>-0.6173</v>
       </c>
       <c r="V6" t="n">
         <v>0.1400999999999998</v>
@@ -955,13 +955,13 @@
         <v>6</v>
       </c>
       <c r="D7" t="n">
-        <v>2.238600000000001</v>
+        <v>2.8206</v>
       </c>
       <c r="E7" t="n">
-        <v>1.947900000000001</v>
+        <v>1.480899999999999</v>
       </c>
       <c r="F7" t="n">
-        <v>0.2907999999999999</v>
+        <v>1.3395</v>
       </c>
       <c r="G7" t="n">
         <v>-0.8077000000000005</v>
@@ -1000,13 +1000,13 @@
         <v>9.553800000000001</v>
       </c>
       <c r="S7" t="n">
-        <v>1.6573</v>
+        <v>2.2389</v>
       </c>
       <c r="T7" t="n">
-        <v>1.0545</v>
+        <v>0.5876</v>
       </c>
       <c r="U7" t="n">
-        <v>0.6025999999999998</v>
+        <v>1.6513</v>
       </c>
       <c r="V7" t="n">
         <v>-2.2503</v>
@@ -1033,13 +1033,13 @@
         <v>3</v>
       </c>
       <c r="D8" t="n">
-        <v>2.2323</v>
+        <v>2.3939</v>
       </c>
       <c r="E8" t="n">
         <v>1.5633</v>
       </c>
       <c r="F8" t="n">
-        <v>0.6691</v>
+        <v>0.8306</v>
       </c>
       <c r="G8" t="n">
         <v>2.2682</v>
@@ -1078,13 +1078,13 @@
         <v>0</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.036</v>
+        <v>0.1257</v>
       </c>
       <c r="T8" t="n">
         <v>-0.1437</v>
       </c>
       <c r="U8" t="n">
-        <v>0.1077</v>
+        <v>0.2694</v>
       </c>
       <c r="V8" t="n">
         <v>0</v>
@@ -1111,13 +1111,13 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>0.5367</v>
+        <v>0.4074</v>
       </c>
       <c r="E9" t="n">
         <v>0.4257</v>
       </c>
       <c r="F9" t="n">
-        <v>0.111</v>
+        <v>-0.0183</v>
       </c>
       <c r="G9" t="n">
         <v>0.3356</v>
@@ -1156,13 +1156,13 @@
         <v>0.2275</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.0264</v>
+        <v>-0.1556</v>
       </c>
       <c r="T9" t="n">
         <v>-0.1437</v>
       </c>
       <c r="U9" t="n">
-        <v>0.1173</v>
+        <v>-0.012</v>
       </c>
       <c r="V9" t="n">
         <v>0</v>
@@ -1189,13 +1189,13 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>0.1772</v>
+        <v>0.2095</v>
       </c>
       <c r="E10" t="n">
         <v>0</v>
       </c>
       <c r="F10" t="n">
-        <v>0.1772</v>
+        <v>0.2095</v>
       </c>
       <c r="G10" t="n">
         <v>0.1556</v>
@@ -1234,13 +1234,13 @@
         <v>0</v>
       </c>
       <c r="S10" t="n">
-        <v>0.0215</v>
+        <v>0.0539</v>
       </c>
       <c r="T10" t="n">
         <v>0</v>
       </c>
       <c r="U10" t="n">
-        <v>0.0215</v>
+        <v>0.0539</v>
       </c>
       <c r="V10" t="n">
         <v>0</v>
@@ -1255,7 +1255,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>A. LEN</t>
+          <t>F. CAMPAZZO</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1264,76 +1264,76 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="D11" t="n">
-        <v>-3.2396</v>
+        <v>-0.4074000000000018</v>
       </c>
       <c r="E11" t="n">
-        <v>-0.4763999999999999</v>
+        <v>5.551399999999999</v>
       </c>
       <c r="F11" t="n">
-        <v>-2.7634</v>
+        <v>-5.9588</v>
       </c>
       <c r="G11" t="n">
-        <v>-4.394500000000001</v>
+        <v>10.3755</v>
       </c>
       <c r="H11" t="n">
-        <v>-1.7174</v>
+        <v>-1.6488</v>
       </c>
       <c r="I11" t="n">
-        <v>-2.6771</v>
+        <v>12.0243</v>
       </c>
       <c r="J11" t="n">
-        <v>-0.4429999999999999</v>
+        <v>19.1248</v>
       </c>
       <c r="K11" t="n">
-        <v>-0.3352999999999999</v>
+        <v>4.0184</v>
       </c>
       <c r="L11" t="n">
-        <v>-0.1076</v>
+        <v>15.1064</v>
       </c>
       <c r="M11" t="n">
-        <v>-3.9514</v>
+        <v>-8.7494</v>
       </c>
       <c r="N11" t="n">
-        <v>-1.3822</v>
+        <v>-5.6671</v>
       </c>
       <c r="O11" t="n">
-        <v>-2.5694</v>
+        <v>-3.0821</v>
       </c>
       <c r="P11" t="n">
-        <v>1.5924</v>
+        <v>-8.1891</v>
       </c>
       <c r="Q11" t="n">
-        <v>-3.4122</v>
+        <v>-17.288</v>
       </c>
       <c r="R11" t="n">
-        <v>5.0044</v>
+        <v>9.0989</v>
       </c>
       <c r="S11" t="n">
-        <v>1.286</v>
+        <v>-0.8887</v>
       </c>
       <c r="T11" t="n">
-        <v>0.1083999999999999</v>
+        <v>-1.666</v>
       </c>
       <c r="U11" t="n">
-        <v>1.1775</v>
+        <v>0.7773</v>
       </c>
       <c r="V11" t="n">
-        <v>-1.7235</v>
+        <v>-1.7052</v>
       </c>
       <c r="W11" t="n">
-        <v>3.2703</v>
+        <v>5.3806</v>
       </c>
       <c r="X11" t="n">
-        <v>-4.9938</v>
+        <v>-7.0857</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>F. CAMPAZZO</t>
+          <t>A. LEN</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1342,70 +1342,70 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="D12" t="n">
-        <v>-5.171900000000001</v>
+        <v>-4.0107</v>
       </c>
       <c r="E12" t="n">
-        <v>2.0941</v>
+        <v>-1.1767</v>
       </c>
       <c r="F12" t="n">
-        <v>-7.2661</v>
+        <v>-2.833899999999999</v>
       </c>
       <c r="G12" t="n">
-        <v>10.3755</v>
+        <v>-4.394500000000001</v>
       </c>
       <c r="H12" t="n">
-        <v>-1.6488</v>
+        <v>-1.7174</v>
       </c>
       <c r="I12" t="n">
-        <v>12.0243</v>
+        <v>-2.6771</v>
       </c>
       <c r="J12" t="n">
-        <v>19.1248</v>
+        <v>-0.4429999999999999</v>
       </c>
       <c r="K12" t="n">
-        <v>4.0184</v>
+        <v>-0.3352999999999999</v>
       </c>
       <c r="L12" t="n">
-        <v>15.1064</v>
+        <v>-0.1076</v>
       </c>
       <c r="M12" t="n">
-        <v>-8.7494</v>
+        <v>-3.9514</v>
       </c>
       <c r="N12" t="n">
-        <v>-5.6671</v>
+        <v>-1.3822</v>
       </c>
       <c r="O12" t="n">
-        <v>-3.0821</v>
+        <v>-2.5694</v>
       </c>
       <c r="P12" t="n">
-        <v>-8.1891</v>
+        <v>1.5924</v>
       </c>
       <c r="Q12" t="n">
-        <v>-17.288</v>
+        <v>-3.4122</v>
       </c>
       <c r="R12" t="n">
-        <v>9.0989</v>
+        <v>5.0044</v>
       </c>
       <c r="S12" t="n">
-        <v>-5.6533</v>
+        <v>0.5149</v>
       </c>
       <c r="T12" t="n">
-        <v>-5.1233</v>
+        <v>-0.5921000000000001</v>
       </c>
       <c r="U12" t="n">
-        <v>-0.53</v>
+        <v>1.107</v>
       </c>
       <c r="V12" t="n">
-        <v>-1.7052</v>
+        <v>-1.7235</v>
       </c>
       <c r="W12" t="n">
-        <v>5.3806</v>
+        <v>3.2703</v>
       </c>
       <c r="X12" t="n">
-        <v>-7.0857</v>
+        <v>-4.9938</v>
       </c>
     </row>
     <row r="13">
@@ -1423,13 +1423,13 @@
         <v>6</v>
       </c>
       <c r="D13" t="n">
-        <v>-5.6568</v>
+        <v>-4.2917</v>
       </c>
       <c r="E13" t="n">
-        <v>-5.930499999999999</v>
+        <v>-4.224200000000002</v>
       </c>
       <c r="F13" t="n">
-        <v>0.2737000000000001</v>
+        <v>-0.0673999999999999</v>
       </c>
       <c r="G13" t="n">
         <v>-1.7038</v>
@@ -1468,13 +1468,13 @@
         <v>10.0088</v>
       </c>
       <c r="S13" t="n">
-        <v>-0.4190999999999999</v>
+        <v>0.9459</v>
       </c>
       <c r="T13" t="n">
-        <v>-2.5611</v>
+        <v>-0.855</v>
       </c>
       <c r="U13" t="n">
-        <v>2.1419</v>
+        <v>1.8006</v>
       </c>
       <c r="V13" t="n">
         <v>3.7454</v>
@@ -1501,13 +1501,13 @@
         <v>6</v>
       </c>
       <c r="D14" t="n">
-        <v>-8.8002</v>
+        <v>-7.194000000000001</v>
       </c>
       <c r="E14" t="n">
-        <v>-2.4843</v>
+        <v>-1.9005</v>
       </c>
       <c r="F14" t="n">
-        <v>-6.3161</v>
+        <v>-5.2937</v>
       </c>
       <c r="G14" t="n">
         <v>-4.9478</v>
@@ -1546,13 +1546,13 @@
         <v>4.0944</v>
       </c>
       <c r="S14" t="n">
-        <v>-2.2436</v>
+        <v>-0.6375000000000002</v>
       </c>
       <c r="T14" t="n">
-        <v>-0.622</v>
+        <v>-0.03839999999999991</v>
       </c>
       <c r="U14" t="n">
-        <v>-1.6216</v>
+        <v>-0.5991</v>
       </c>
       <c r="V14" t="n">
         <v>-3.4287</v>
@@ -1579,13 +1579,13 @@
         <v>6</v>
       </c>
       <c r="D15" t="n">
-        <v>-9.6943</v>
+        <v>-9.3637</v>
       </c>
       <c r="E15" t="n">
-        <v>-7.6504</v>
+        <v>-7.4168</v>
       </c>
       <c r="F15" t="n">
-        <v>-2.0439</v>
+        <v>-1.9469</v>
       </c>
       <c r="G15" t="n">
         <v>-7.5288</v>
@@ -1624,13 +1624,13 @@
         <v>2.7296</v>
       </c>
       <c r="S15" t="n">
-        <v>-1.3719</v>
+        <v>-1.0415</v>
       </c>
       <c r="T15" t="n">
-        <v>-1.4484</v>
+        <v>-1.215</v>
       </c>
       <c r="U15" t="n">
-        <v>0.07640000000000002</v>
+        <v>0.1735</v>
       </c>
       <c r="V15" t="n">
         <v>-1.2484</v>
@@ -1657,13 +1657,13 @@
         <v>6</v>
       </c>
       <c r="D16" t="n">
-        <v>37.83880000000001</v>
+        <v>42.09</v>
       </c>
       <c r="E16" t="n">
-        <v>25.7022</v>
+        <v>26.06179999999999</v>
       </c>
       <c r="F16" t="n">
-        <v>12.1367</v>
+        <v>16.02810000000001</v>
       </c>
       <c r="G16" t="n">
         <v>17.45599999999999</v>
@@ -1681,7 +1681,7 @@
         <v>25.2518</v>
       </c>
       <c r="L16" t="n">
-        <v>34.04889999999999</v>
+        <v>34.0489</v>
       </c>
       <c r="M16" t="n">
         <v>-41.8442</v>
@@ -1702,13 +1702,13 @@
         <v>80.75280000000001</v>
       </c>
       <c r="S16" t="n">
-        <v>11.5536</v>
+        <v>15.8038</v>
       </c>
       <c r="T16" t="n">
-        <v>1.504799999999999</v>
+        <v>1.8639</v>
       </c>
       <c r="U16" t="n">
-        <v>10.0481</v>
+        <v>13.9396</v>
       </c>
       <c r="V16" t="n">
         <v>-1.406899999999999</v>
